--- a/data/safety_training.xlsx
+++ b/data/safety_training.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8" uniqueCount="8">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="13" uniqueCount="13">
   <si>
     <t>ID</t>
   </si>
@@ -38,6 +38,21 @@
   </si>
   <si>
     <t>Created_At</t>
+  </si>
+  <si>
+    <t>d8cff1ff7b7e441b82227b732abc6a8b</t>
+  </si>
+  <si>
+    <t>2025-11-12</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Incident recall </t>
+  </si>
+  <si>
+    <t>Humphry Lungu</t>
+  </si>
+  <si>
+    <t>2025-12-02T20:13:15.679218</t>
   </si>
 </sst>
 </file>
@@ -395,7 +410,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H1"/>
+  <dimension ref="A1:H2"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:8">
@@ -424,6 +439,23 @@
         <v>7</v>
       </c>
     </row>
+    <row r="2" spans="1:8">
+      <c r="A2" t="s">
+        <v>8</v>
+      </c>
+      <c r="B2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D2" t="s">
+        <v>10</v>
+      </c>
+      <c r="E2" t="s">
+        <v>11</v>
+      </c>
+      <c r="H2" t="s">
+        <v>12</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
